--- a/image source/milk_record.xlsx
+++ b/image source/milk_record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shifuu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shifuu\Desktop\Project\kinder-track\image source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A551CD51-07D8-46A9-B6CB-13AA91F869B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD218B8C-5384-427D-BDB2-A842629426ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บันทึกการดื่มนม" sheetId="1" r:id="rId1"/>
@@ -366,17 +366,13 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -387,16 +383,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -715,7 +715,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="19"/>
@@ -757,7 +757,7 @@
       <c r="AL1" s="19"/>
     </row>
     <row r="2" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="19"/>
@@ -799,58 +799,58 @@
       <c r="AL2" s="19"/>
     </row>
     <row r="3" spans="1:38" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="24"/>
-      <c r="AB3" s="24"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="24"/>
-      <c r="AF3" s="24"/>
-      <c r="AG3" s="24"/>
-      <c r="AH3" s="24"/>
-      <c r="AI3" s="24"/>
-      <c r="AJ3" s="23" t="s">
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="22"/>
+      <c r="AC3" s="22"/>
+      <c r="AD3" s="22"/>
+      <c r="AE3" s="22"/>
+      <c r="AF3" s="22"/>
+      <c r="AG3" s="22"/>
+      <c r="AH3" s="22"/>
+      <c r="AI3" s="22"/>
+      <c r="AJ3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="AK3" s="25" t="s">
+      <c r="AK3" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="21" t="s">
+      <c r="AL3" s="25" t="s">
         <v>9</v>
       </c>
     </row>
@@ -952,9 +952,9 @@
       <c r="AI4" s="2">
         <v>31</v>
       </c>
-      <c r="AJ4" s="24"/>
-      <c r="AK4" s="24"/>
-      <c r="AL4" s="24"/>
+      <c r="AJ4" s="22"/>
+      <c r="AK4" s="22"/>
+      <c r="AL4" s="22"/>
     </row>
     <row r="5" spans="1:38" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
@@ -2877,7 +2877,7 @@
       <c r="AL44" s="9"/>
     </row>
     <row r="45" spans="1:38" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="27" t="s">
         <v>10</v>
       </c>
       <c r="B45" s="19"/>
@@ -3018,7 +3018,7 @@
       <c r="AL45" s="13"/>
     </row>
     <row r="47" spans="1:38" ht="22.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="30" t="s">
         <v>11</v>
       </c>
       <c r="B47" s="19"/>
@@ -3027,7 +3027,7 @@
       <c r="E47" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F47" s="22" t="e">
+      <c r="F47" s="29" t="e">
         <f>ดื่มนม (มาโรงเรียน)</f>
         <v>#NAME?</v>
       </c>
@@ -3037,7 +3037,7 @@
       <c r="J47" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="K47" s="22" t="e">
+      <c r="K47" s="29" t="e">
         <f>ขาด / ไม่ได้ดื่มนม</f>
         <v>#NAME?</v>
       </c>
@@ -3048,6 +3048,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A1:AL1"/>
@@ -3055,13 +3062,6 @@
     <mergeCell ref="AL3:AL4"/>
     <mergeCell ref="E3:AI3"/>
     <mergeCell ref="A2:AL2"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="K47:O47"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -3084,7 +3084,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="20" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="19"/>
@@ -3105,7 +3105,7 @@
       <c r="Q1" s="19"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="18" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="19"/>
